--- a/Data/FlightPlan/FPL_20SEP26.xlsx
+++ b/Data/FlightPlan/FPL_20SEP26.xlsx
@@ -107,483 +107,486 @@
     <t>08:50</t>
   </si>
   <si>
+    <t>12:46</t>
+  </si>
+  <si>
+    <t>VII</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>15:50</t>
+  </si>
+  <si>
+    <t>16:20</t>
+  </si>
+  <si>
+    <t>18:10</t>
+  </si>
+  <si>
+    <t>DAD</t>
+  </si>
+  <si>
+    <t>20:40</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
+    <t>VN-A202</t>
+  </si>
+  <si>
+    <t>11:40</t>
+  </si>
+  <si>
+    <t>14:55</t>
+  </si>
+  <si>
+    <t>DEL</t>
+  </si>
+  <si>
+    <t>22:55</t>
+  </si>
+  <si>
+    <t>21/09/26</t>
+  </si>
+  <si>
+    <t>00:05</t>
+  </si>
+  <si>
+    <t>06:35</t>
+  </si>
+  <si>
+    <t>VN-A203</t>
+  </si>
+  <si>
+    <t>HAN</t>
+  </si>
+  <si>
+    <t>SIN</t>
+  </si>
+  <si>
+    <t>09:35</t>
+  </si>
+  <si>
+    <t>13:55</t>
+  </si>
+  <si>
+    <t>17:25</t>
+  </si>
+  <si>
+    <t>CXR</t>
+  </si>
+  <si>
+    <t>18:15</t>
+  </si>
+  <si>
+    <t>20:05</t>
+  </si>
+  <si>
+    <t>05:35</t>
+  </si>
+  <si>
+    <t>VN-A500</t>
+  </si>
+  <si>
+    <t>PQC</t>
+  </si>
+  <si>
+    <t>04:05</t>
+  </si>
+  <si>
+    <t>07:35</t>
+  </si>
+  <si>
+    <t>08:07</t>
+  </si>
+  <si>
+    <t>08:30</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
+    <t>14:50</t>
+  </si>
+  <si>
+    <t>16:10</t>
+  </si>
+  <si>
+    <t>17:40</t>
+  </si>
+  <si>
+    <t>19:50</t>
+  </si>
+  <si>
+    <t>VN-A521</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>07:34</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>10:25</t>
+  </si>
+  <si>
+    <t>13:30</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>15:15</t>
+  </si>
+  <si>
+    <t>06:55</t>
+  </si>
+  <si>
+    <t>VN-A522</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>12:05</t>
+  </si>
+  <si>
+    <t>13:05</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>19:30</t>
+  </si>
+  <si>
+    <t>20:35</t>
+  </si>
+  <si>
+    <t>22:40</t>
+  </si>
+  <si>
+    <t>00:50</t>
+  </si>
+  <si>
+    <t>VN-A523</t>
+  </si>
+  <si>
+    <t>KHH</t>
+  </si>
+  <si>
+    <t>07:30</t>
+  </si>
+  <si>
+    <t>12:40</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>01:00</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>VN-A524</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>09:40</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
+    <t>VCA</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>15:20</t>
+  </si>
+  <si>
+    <t>16:50</t>
+  </si>
+  <si>
+    <t>VN-A526</t>
+  </si>
+  <si>
+    <t>NGO</t>
+  </si>
+  <si>
+    <t>09:25</t>
+  </si>
+  <si>
+    <t>12:50</t>
+  </si>
+  <si>
+    <t>TPE</t>
+  </si>
+  <si>
+    <t>14:25</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>20:55</t>
+  </si>
+  <si>
+    <t>NRT</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>VN-A529</t>
+  </si>
+  <si>
+    <t>DPS</t>
+  </si>
+  <si>
+    <t>08:45</t>
+  </si>
+  <si>
+    <t>13:35</t>
+  </si>
+  <si>
+    <t>14:35</t>
+  </si>
+  <si>
+    <t>BOM</t>
+  </si>
+  <si>
+    <t>19:40</t>
+  </si>
+  <si>
+    <t>23:15</t>
+  </si>
+  <si>
+    <t>00:15</t>
+  </si>
+  <si>
+    <t>07:15</t>
+  </si>
+  <si>
+    <t>VN-A534</t>
+  </si>
+  <si>
+    <t>HPH</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>10:45</t>
+  </si>
+  <si>
+    <t>15:55</t>
+  </si>
+  <si>
+    <t>16:40</t>
+  </si>
+  <si>
+    <t>VN-A535</t>
+  </si>
+  <si>
+    <t>10:20</t>
+  </si>
+  <si>
+    <t>16:15</t>
+  </si>
+  <si>
+    <t>18:25</t>
+  </si>
+  <si>
+    <t>22:10</t>
+  </si>
+  <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>23:10</t>
+  </si>
+  <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>23:30</t>
+  </si>
+  <si>
+    <t>VN-A536</t>
+  </si>
+  <si>
+    <t>10:55</t>
+  </si>
+  <si>
+    <t>HGH</t>
+  </si>
+  <si>
+    <t>20:20</t>
+  </si>
+  <si>
+    <t>21:35</t>
+  </si>
+  <si>
+    <t>00:10</t>
+  </si>
+  <si>
+    <t>03:10</t>
+  </si>
+  <si>
+    <t>09:50</t>
+  </si>
+  <si>
+    <t>VN-A539</t>
+  </si>
+  <si>
+    <t>HUI</t>
+  </si>
+  <si>
+    <t>06:52</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>11:55</t>
+  </si>
+  <si>
+    <t>12:25</t>
+  </si>
+  <si>
+    <t>13:50</t>
+  </si>
+  <si>
+    <t>15:35</t>
+  </si>
+  <si>
+    <t>16:05</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>VDH</t>
+  </si>
+  <si>
+    <t>19:15</t>
+  </si>
+  <si>
+    <t>19:45</t>
+  </si>
+  <si>
+    <t>21:20</t>
+  </si>
+  <si>
+    <t>VN-A542</t>
+  </si>
+  <si>
+    <t>09:30</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>BKK</t>
+  </si>
+  <si>
+    <t>13:15</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>17:15</t>
+  </si>
+  <si>
+    <t>20:10</t>
+  </si>
+  <si>
+    <t>02:35</t>
+  </si>
+  <si>
+    <t>VN-A543</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>10:37</t>
+  </si>
+  <si>
+    <t>DLI</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>23:55</t>
+  </si>
+  <si>
+    <t>06:15</t>
+  </si>
+  <si>
+    <t>VN-A544</t>
+  </si>
+  <si>
+    <t>05:05</t>
+  </si>
+  <si>
+    <t>06:20</t>
+  </si>
+  <si>
+    <t>06:34</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>CGK</t>
+  </si>
+  <si>
     <t>12:30</t>
   </si>
   <si>
-    <t>VII</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>15:50</t>
-  </si>
-  <si>
-    <t>16:20</t>
-  </si>
-  <si>
-    <t>18:10</t>
-  </si>
-  <si>
-    <t>DAD</t>
-  </si>
-  <si>
-    <t>20:40</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
-    <t>VN-A202</t>
-  </si>
-  <si>
-    <t>11:40</t>
-  </si>
-  <si>
-    <t>14:55</t>
-  </si>
-  <si>
-    <t>DEL</t>
-  </si>
-  <si>
-    <t>22:55</t>
-  </si>
-  <si>
-    <t>21/09/26</t>
-  </si>
-  <si>
-    <t>00:05</t>
-  </si>
-  <si>
-    <t>06:35</t>
-  </si>
-  <si>
-    <t>VN-A203</t>
-  </si>
-  <si>
-    <t>HAN</t>
-  </si>
-  <si>
-    <t>SIN</t>
-  </si>
-  <si>
-    <t>09:35</t>
-  </si>
-  <si>
-    <t>13:55</t>
-  </si>
-  <si>
-    <t>17:25</t>
-  </si>
-  <si>
-    <t>CXR</t>
-  </si>
-  <si>
-    <t>18:15</t>
-  </si>
-  <si>
-    <t>20:05</t>
-  </si>
-  <si>
-    <t>05:35</t>
-  </si>
-  <si>
-    <t>VN-A500</t>
-  </si>
-  <si>
-    <t>PQC</t>
-  </si>
-  <si>
-    <t>04:05</t>
-  </si>
-  <si>
-    <t>07:35</t>
-  </si>
-  <si>
-    <t>08:07</t>
-  </si>
-  <si>
-    <t>08:30</t>
-  </si>
-  <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>14:20</t>
-  </si>
-  <si>
-    <t>14:50</t>
-  </si>
-  <si>
-    <t>16:10</t>
-  </si>
-  <si>
-    <t>17:40</t>
-  </si>
-  <si>
-    <t>19:50</t>
-  </si>
-  <si>
-    <t>VN-A521</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>07:34</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>10:25</t>
-  </si>
-  <si>
-    <t>13:30</t>
-  </si>
-  <si>
-    <t>14:30</t>
-  </si>
-  <si>
-    <t>15:15</t>
-  </si>
-  <si>
-    <t>06:55</t>
-  </si>
-  <si>
-    <t>VN-A522</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>12:05</t>
-  </si>
-  <si>
-    <t>13:05</t>
-  </si>
-  <si>
-    <t>13:45</t>
-  </si>
-  <si>
-    <t>15:45</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>19:30</t>
-  </si>
-  <si>
-    <t>20:35</t>
-  </si>
-  <si>
-    <t>22:40</t>
-  </si>
-  <si>
-    <t>00:50</t>
-  </si>
-  <si>
-    <t>VN-A523</t>
-  </si>
-  <si>
-    <t>KHH</t>
-  </si>
-  <si>
-    <t>07:30</t>
-  </si>
-  <si>
-    <t>12:40</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>01:00</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>VN-A524</t>
-  </si>
-  <si>
-    <t>07:00</t>
-  </si>
-  <si>
-    <t>09:40</t>
-  </si>
-  <si>
-    <t>10:15</t>
-  </si>
-  <si>
-    <t>VCA</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
-    <t>15:20</t>
-  </si>
-  <si>
-    <t>16:50</t>
-  </si>
-  <si>
-    <t>VN-A526</t>
-  </si>
-  <si>
-    <t>NGO</t>
-  </si>
-  <si>
-    <t>09:25</t>
-  </si>
-  <si>
-    <t>12:50</t>
-  </si>
-  <si>
-    <t>TPE</t>
-  </si>
-  <si>
-    <t>14:25</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>19:00</t>
-  </si>
-  <si>
-    <t>20:55</t>
-  </si>
-  <si>
-    <t>NRT</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
-    <t>VN-A529</t>
-  </si>
-  <si>
-    <t>DPS</t>
-  </si>
-  <si>
-    <t>08:45</t>
-  </si>
-  <si>
-    <t>13:35</t>
-  </si>
-  <si>
-    <t>14:35</t>
-  </si>
-  <si>
-    <t>BOM</t>
-  </si>
-  <si>
-    <t>19:40</t>
-  </si>
-  <si>
-    <t>23:15</t>
-  </si>
-  <si>
-    <t>00:15</t>
-  </si>
-  <si>
-    <t>07:15</t>
-  </si>
-  <si>
-    <t>VN-A534</t>
-  </si>
-  <si>
-    <t>HPH</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>10:45</t>
-  </si>
-  <si>
-    <t>15:55</t>
-  </si>
-  <si>
-    <t>16:40</t>
-  </si>
-  <si>
-    <t>VN-A535</t>
-  </si>
-  <si>
-    <t>10:20</t>
-  </si>
-  <si>
-    <t>16:15</t>
-  </si>
-  <si>
-    <t>18:25</t>
-  </si>
-  <si>
-    <t>22:10</t>
-  </si>
-  <si>
-    <t>20:25</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>23:10</t>
-  </si>
-  <si>
-    <t>06:40</t>
-  </si>
-  <si>
-    <t>23:30</t>
-  </si>
-  <si>
-    <t>VN-A536</t>
-  </si>
-  <si>
-    <t>10:55</t>
-  </si>
-  <si>
-    <t>HGH</t>
-  </si>
-  <si>
-    <t>20:20</t>
-  </si>
-  <si>
-    <t>21:35</t>
-  </si>
-  <si>
-    <t>00:10</t>
-  </si>
-  <si>
-    <t>03:10</t>
-  </si>
-  <si>
-    <t>09:50</t>
-  </si>
-  <si>
-    <t>VN-A539</t>
-  </si>
-  <si>
-    <t>HUI</t>
-  </si>
-  <si>
-    <t>06:52</t>
-  </si>
-  <si>
-    <t>07:25</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>11:55</t>
-  </si>
-  <si>
-    <t>12:25</t>
-  </si>
-  <si>
-    <t>13:50</t>
-  </si>
-  <si>
-    <t>15:35</t>
-  </si>
-  <si>
-    <t>16:05</t>
-  </si>
-  <si>
-    <t>17:10</t>
-  </si>
-  <si>
-    <t>VDH</t>
-  </si>
-  <si>
-    <t>19:15</t>
-  </si>
-  <si>
-    <t>19:45</t>
-  </si>
-  <si>
-    <t>21:20</t>
-  </si>
-  <si>
-    <t>VN-A542</t>
-  </si>
-  <si>
-    <t>09:30</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>BKK</t>
-  </si>
-  <si>
-    <t>13:15</t>
-  </si>
-  <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>17:15</t>
-  </si>
-  <si>
-    <t>20:10</t>
-  </si>
-  <si>
-    <t>02:35</t>
-  </si>
-  <si>
-    <t>VN-A543</t>
-  </si>
-  <si>
-    <t>09:55</t>
-  </si>
-  <si>
-    <t>10:37</t>
-  </si>
-  <si>
-    <t>DLI</t>
-  </si>
-  <si>
-    <t>17:55</t>
-  </si>
-  <si>
-    <t>23:55</t>
-  </si>
-  <si>
-    <t>06:15</t>
-  </si>
-  <si>
-    <t>VN-A544</t>
-  </si>
-  <si>
-    <t>05:05</t>
-  </si>
-  <si>
-    <t>06:20</t>
-  </si>
-  <si>
-    <t>06:34</t>
-  </si>
-  <si>
-    <t>06:50</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>CGK</t>
-  </si>
-  <si>
     <t>BLR</t>
   </si>
   <si>
@@ -743,6 +746,9 @@
     <t>VN-A629</t>
   </si>
   <si>
+    <t>11:17</t>
+  </si>
+  <si>
     <t>11:45</t>
   </si>
   <si>
@@ -869,6 +875,9 @@
     <t>06:45</t>
   </si>
   <si>
+    <t>09:12</t>
+  </si>
+  <si>
     <t>15:05</t>
   </si>
   <si>
@@ -911,6 +920,9 @@
     <t>07:45</t>
   </si>
   <si>
+    <t>07:56</t>
+  </si>
+  <si>
     <t>08:15</t>
   </si>
   <si>
@@ -974,6 +986,9 @@
     <t>06:30</t>
   </si>
   <si>
+    <t>07:38</t>
+  </si>
+  <si>
     <t>VN-A650</t>
   </si>
   <si>
@@ -983,6 +998,9 @@
     <t>05:20</t>
   </si>
   <si>
+    <t>08:26</t>
+  </si>
+  <si>
     <t>23:00</t>
   </si>
   <si>
@@ -1019,6 +1037,9 @@
     <t>06:05</t>
   </si>
   <si>
+    <t>07:49</t>
+  </si>
+  <si>
     <t>18:55</t>
   </si>
   <si>
@@ -1064,6 +1085,9 @@
     <t>HIJ</t>
   </si>
   <si>
+    <t>12:49</t>
+  </si>
+  <si>
     <t>VN-A667</t>
   </si>
   <si>
@@ -1085,7 +1109,10 @@
     <t>VN-A669</t>
   </si>
   <si>
-    <t>07:07</t>
+    <t>07:09</t>
+  </si>
+  <si>
+    <t>08:24</t>
   </si>
   <si>
     <t>11:00</t>
@@ -1097,12 +1124,18 @@
     <t>VN-A670</t>
   </si>
   <si>
+    <t>08:23</t>
+  </si>
+  <si>
     <t>VN-A671</t>
   </si>
   <si>
     <t>09:10</t>
   </si>
   <si>
+    <t>09:05</t>
+  </si>
+  <si>
     <t>11:50</t>
   </si>
   <si>
@@ -1145,6 +1178,9 @@
     <t>VN-A676</t>
   </si>
   <si>
+    <t>09:04</t>
+  </si>
+  <si>
     <t>SAI</t>
   </si>
   <si>
@@ -1187,7 +1223,7 @@
     <t>VN-A687</t>
   </si>
   <si>
-    <t>09:05</t>
+    <t>08:52</t>
   </si>
   <si>
     <t>03:05</t>
@@ -1229,6 +1265,9 @@
     <t>NQZ</t>
   </si>
   <si>
+    <t>03:25</t>
+  </si>
+  <si>
     <t>VN-A812</t>
   </si>
   <si>
@@ -1247,7 +1286,7 @@
     <t>Total Record(s): 397</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Sep 20, 2026 06:19</t>
+    <t xml:space="preserve">Generated on  Sep 20, 2026 07:29</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -4783,7 +4822,7 @@
         <v>52</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>32</v>
+        <v>191</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -4843,13 +4882,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H107" s="8">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -4873,16 +4912,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G108" s="8">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="H108" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -4915,7 +4954,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -4927,7 +4966,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="J110" s="7">
         <v>31</v>
@@ -4948,7 +4987,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -4963,7 +5002,7 @@
         <v>110</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
@@ -4981,7 +5020,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -4996,7 +5035,7 @@
         <v>42</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
@@ -5014,7 +5053,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -5047,7 +5086,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5059,10 +5098,10 @@
         <v>104</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -5080,7 +5119,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5095,7 +5134,7 @@
         <v>125</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5113,7 +5152,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5125,10 +5164,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -5161,7 +5200,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5194,7 +5233,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5206,10 +5245,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5227,7 +5266,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5239,10 +5278,10 @@
         <v>38</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>32</v>
+        <v>191</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5260,7 +5299,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5293,7 +5332,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5305,7 +5344,7 @@
         <v>38</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c t="s" r="J122" s="7">
         <v>96</v>
@@ -5326,7 +5365,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5338,10 +5377,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
@@ -5359,7 +5398,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5368,7 +5407,7 @@
         <v>50</v>
       </c>
       <c t="s" r="H124" s="8">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="I124" s="7">
         <v>166</v>
@@ -5392,13 +5431,13 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G125" s="8">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c t="s" r="H125" s="8">
         <v>50</v>
@@ -5407,7 +5446,7 @@
         <v>150</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -5440,7 +5479,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5473,7 +5512,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5485,10 +5524,10 @@
         <v>180</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -5506,7 +5545,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5539,7 +5578,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5548,13 +5587,13 @@
         <v>50</v>
       </c>
       <c t="s" r="H130" s="8">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5587,13 +5626,13 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G132" s="8">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="H132" s="8">
         <v>16</v>
@@ -5620,7 +5659,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -5653,7 +5692,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5665,10 +5704,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -5701,7 +5740,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -5713,10 +5752,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -5734,7 +5773,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -5767,7 +5806,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5782,7 +5821,7 @@
         <v>166</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -5811,11 +5850,11 @@
         <v>7621</v>
       </c>
       <c t="s" r="C140" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -5844,11 +5883,11 @@
         <v>7614</v>
       </c>
       <c t="s" r="C141" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -5860,7 +5899,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c t="s" r="J141" s="7">
         <v>165</v>
@@ -5877,11 +5916,11 @@
         <v>7614</v>
       </c>
       <c t="s" r="C142" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -5890,7 +5929,7 @@
         <v>50</v>
       </c>
       <c t="s" r="H142" s="8">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c t="s" r="I142" s="7">
         <v>70</v>
@@ -5922,14 +5961,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B144" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="C144" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -5966,7 +6005,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -5978,10 +6017,10 @@
         <v>104</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -5999,7 +6038,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6011,10 +6050,10 @@
         <v>38</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -6032,7 +6071,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6044,10 +6083,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -6065,7 +6104,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6074,10 +6113,10 @@
         <v>50</v>
       </c>
       <c t="s" r="H148" s="8">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="J148" s="7">
         <v>64</v>
@@ -6113,19 +6152,19 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G150" s="8">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="H150" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="J150" s="7">
         <v>24</v>
@@ -6146,7 +6185,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6155,13 +6194,13 @@
         <v>50</v>
       </c>
       <c t="s" r="H151" s="8">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="I151" s="7">
         <v>76</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6179,13 +6218,13 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G152" s="8">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="H152" s="8">
         <v>50</v>
@@ -6212,7 +6251,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6224,7 +6263,7 @@
         <v>109</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J153" s="7">
         <v>118</v>
@@ -6260,7 +6299,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6272,10 +6311,10 @@
         <v>117</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6293,7 +6332,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6341,7 +6380,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6353,10 +6392,10 @@
         <v>120</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
@@ -6374,7 +6413,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6407,7 +6446,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6419,7 +6458,7 @@
         <v>130</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="J160" s="7">
         <v>70</v>
@@ -6440,7 +6479,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -6455,7 +6494,7 @@
         <v>148</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6473,7 +6512,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6482,7 +6521,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H162" s="8">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="I162" s="7">
         <v>97</v>
@@ -6521,7 +6560,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6536,11 +6575,13 @@
         <v>21</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
-      <c r="M164" s="7"/>
+      <c t="s" r="M164" s="7">
+        <v>245</v>
+      </c>
     </row>
     <row r="165" ht="15" customHeight="1">
       <c t="s" r="A165" s="6">
@@ -6554,7 +6595,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -6566,7 +6607,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c t="s" r="J165" s="7">
         <v>53</v>
@@ -6587,7 +6628,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -6602,7 +6643,7 @@
         <v>123</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -6620,7 +6661,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6629,10 +6670,10 @@
         <v>50</v>
       </c>
       <c t="s" r="H167" s="8">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c t="s" r="J167" s="7">
         <v>165</v>
@@ -6653,13 +6694,13 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G168" s="8">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c t="s" r="H168" s="8">
         <v>50</v>
@@ -6668,7 +6709,7 @@
         <v>166</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -6701,7 +6742,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6716,7 +6757,7 @@
         <v>169</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6734,7 +6775,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6767,7 +6808,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -6776,10 +6817,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H172" s="8">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c t="s" r="J172" s="7">
         <v>138</v>
@@ -6800,22 +6841,22 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G173" s="8">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c t="s" r="H173" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -6848,7 +6889,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -6860,7 +6901,7 @@
         <v>38</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c t="s" r="J175" s="7">
         <v>189</v>
@@ -6881,7 +6922,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -6893,7 +6934,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c t="s" r="J176" s="7">
         <v>103</v>
@@ -6914,7 +6955,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -6926,7 +6967,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="J177" s="7">
         <v>172</v>
@@ -6947,7 +6988,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -6980,7 +7021,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -6995,7 +7036,7 @@
         <v>36</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -7013,7 +7054,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7046,7 +7087,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7079,7 +7120,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7127,7 +7168,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7136,7 +7177,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H184" s="8">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="I184" s="7">
         <v>22</v>
@@ -7160,19 +7201,19 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G185" s="8">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="H185" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="J185" s="7">
         <v>114</v>
@@ -7193,7 +7234,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7202,10 +7243,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H186" s="8">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c t="s" r="J186" s="7">
         <v>97</v>
@@ -7226,22 +7267,22 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G187" s="8">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c t="s" r="H187" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -7274,7 +7315,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7286,7 +7327,7 @@
         <v>38</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J189" s="7">
         <v>76</v>
@@ -7307,7 +7348,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7319,10 +7360,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7340,7 +7381,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7352,10 +7393,10 @@
         <v>55</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7373,7 +7414,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7385,7 +7426,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="J192" s="7">
         <v>175</v>
@@ -7406,7 +7447,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7421,7 +7462,7 @@
         <v>116</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7454,7 +7495,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7463,20 +7504,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H195" s="8">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c t="s" r="I195" s="7">
         <v>143</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c t="s" r="K195" s="7">
         <v>101</v>
       </c>
       <c r="L195" s="7"/>
       <c t="s" r="M195" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="196" ht="14.25" customHeight="1">
@@ -7491,29 +7532,29 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G196" s="8">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c t="s" r="H196" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="J196" s="7">
         <v>169</v>
       </c>
       <c t="s" r="K196" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="L196" s="7"/>
       <c t="s" r="M196" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="197" ht="14.25" customHeight="1">
@@ -7528,7 +7569,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7545,13 +7586,9 @@
       <c t="s" r="J197" s="7">
         <v>170</v>
       </c>
-      <c t="s" r="K197" s="7">
-        <v>178</v>
-      </c>
+      <c r="K197" s="7"/>
       <c r="L197" s="7"/>
-      <c t="s" r="M197" s="7">
-        <v>158</v>
-      </c>
+      <c r="M197" s="7"/>
     </row>
     <row r="198" ht="14.25" customHeight="1">
       <c t="s" r="A198" s="6">
@@ -7565,7 +7602,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -7577,7 +7614,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>32</v>
+        <v>191</v>
       </c>
       <c t="s" r="J198" s="7">
         <v>77</v>
@@ -7598,7 +7635,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7607,13 +7644,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H199" s="8">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c t="s" r="I199" s="7">
         <v>134</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -7631,19 +7668,19 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G200" s="8">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c t="s" r="H200" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="J200" s="7">
         <v>87</v>
@@ -7664,7 +7701,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7676,10 +7713,10 @@
         <v>130</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -7697,7 +7734,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7709,10 +7746,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7745,7 +7782,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -7757,7 +7794,7 @@
         <v>33</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c t="s" r="J204" s="7">
         <v>188</v>
@@ -7765,7 +7802,7 @@
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
       <c t="s" r="M204" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="205" ht="15" customHeight="1">
@@ -7780,7 +7817,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7789,10 +7826,10 @@
         <v>33</v>
       </c>
       <c t="s" r="H205" s="8">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c t="s" r="J205" s="7">
         <v>121</v>
@@ -7813,22 +7850,22 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G206" s="8">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c t="s" r="H206" s="8">
         <v>33</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -7846,7 +7883,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7858,7 +7895,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="J207" s="7">
         <v>65</v>
@@ -7879,7 +7916,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -7888,13 +7925,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H208" s="8">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -7912,13 +7949,13 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G209" s="8">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c t="s" r="H209" s="8">
         <v>16</v>
@@ -7927,7 +7964,7 @@
         <v>70</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -7956,17 +7993,17 @@
         <v>31</v>
       </c>
       <c t="s" r="C211" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G211" s="8">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c t="s" r="H211" s="8">
         <v>50</v>
@@ -8008,7 +8045,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8020,14 +8057,16 @@
         <v>104</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
-      <c r="M213" s="7"/>
+      <c t="s" r="M213" s="7">
+        <v>288</v>
+      </c>
     </row>
     <row r="214" ht="14.25" customHeight="1">
       <c t="s" r="A214" s="6">
@@ -8041,7 +8080,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8074,7 +8113,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8089,7 +8128,7 @@
         <v>65</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
@@ -8107,7 +8146,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8119,10 +8158,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8140,7 +8179,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8152,7 +8191,7 @@
         <v>38</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c t="s" r="J217" s="7">
         <v>140</v>
@@ -8173,7 +8212,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8185,10 +8224,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8221,7 +8260,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8236,7 +8275,7 @@
         <v>133</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8254,7 +8293,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8269,7 +8308,7 @@
         <v>25</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8287,7 +8326,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8302,7 +8341,7 @@
         <v>26</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8320,7 +8359,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8332,10 +8371,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8368,7 +8407,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8387,7 +8426,9 @@
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
-      <c r="M225" s="7"/>
+      <c t="s" r="M225" s="7">
+        <v>63</v>
+      </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
       <c t="s" r="A226" s="6">
@@ -8401,7 +8442,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8413,7 +8454,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c t="s" r="J226" s="7">
         <v>103</v>
@@ -8434,7 +8475,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8446,7 +8487,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c t="s" r="J227" s="7">
         <v>24</v>
@@ -8467,7 +8508,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -8482,7 +8523,7 @@
         <v>65</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8500,7 +8541,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8512,10 +8553,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8533,7 +8574,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8545,10 +8586,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
@@ -8581,7 +8622,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8590,18 +8631,18 @@
         <v>50</v>
       </c>
       <c t="s" r="H232" s="8">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
       <c t="s" r="M232" s="7">
-        <v>20</v>
+        <v>303</v>
       </c>
     </row>
     <row r="233" ht="14.25" customHeight="1">
@@ -8616,19 +8657,19 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G233" s="8">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c t="s" r="H233" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c t="s" r="J233" s="7">
         <v>131</v>
@@ -8649,7 +8690,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8661,7 +8702,7 @@
         <v>171</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="J234" s="7">
         <v>65</v>
@@ -8682,7 +8723,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -8730,7 +8771,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -8750,7 +8791,7 @@
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
       <c t="s" r="M237" s="7">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="238" ht="14.25" customHeight="1">
@@ -8765,7 +8806,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -8798,7 +8839,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -8810,10 +8851,10 @@
         <v>154</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -8831,7 +8872,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8864,7 +8905,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -8876,7 +8917,7 @@
         <v>55</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c t="s" r="J241" s="7">
         <v>43</v>
@@ -8897,7 +8938,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -8909,7 +8950,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c t="s" r="J242" s="7">
         <v>174</v>
@@ -8930,7 +8971,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -8942,10 +8983,10 @@
         <v>38</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -8963,7 +9004,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -8975,7 +9016,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c t="s" r="J244" s="7">
         <v>116</v>
@@ -9011,7 +9052,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9023,7 +9064,7 @@
         <v>51</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c t="s" r="J246" s="7">
         <v>103</v>
@@ -9044,7 +9085,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9056,10 +9097,10 @@
         <v>38</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9077,7 +9118,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9086,7 +9127,7 @@
         <v>38</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="I248" s="7">
         <v>77</v>
@@ -9110,13 +9151,13 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G249" s="8">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="H249" s="8">
         <v>38</v>
@@ -9158,7 +9199,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9191,7 +9232,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9206,7 +9247,7 @@
         <v>123</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9224,7 +9265,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9236,7 +9277,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c t="s" r="J253" s="7">
         <v>88</v>
@@ -9257,7 +9298,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -9269,10 +9310,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9305,7 +9346,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9317,14 +9358,16 @@
         <v>16</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
-      <c r="M256" s="7"/>
+      <c t="s" r="M256" s="7">
+        <v>53</v>
+      </c>
     </row>
     <row r="257" ht="14.25" customHeight="1">
       <c t="s" r="A257" s="6">
@@ -9338,7 +9381,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9371,7 +9414,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -9383,7 +9426,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c t="s" r="J258" s="7">
         <v>166</v>
@@ -9404,7 +9447,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9413,13 +9456,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H259" s="8">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c t="s" r="I259" s="7">
         <v>97</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9452,7 +9495,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -9464,7 +9507,7 @@
         <v>38</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c t="s" r="J261" s="7">
         <v>22</v>
@@ -9472,7 +9515,7 @@
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
       <c t="s" r="M261" s="7">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="262" ht="14.25" customHeight="1">
@@ -9487,7 +9530,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9496,10 +9539,10 @@
         <v>38</v>
       </c>
       <c t="s" r="H262" s="8">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c t="s" r="J262" s="7">
         <v>67</v>
@@ -9520,13 +9563,13 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G263" s="8">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c t="s" r="H263" s="8">
         <v>38</v>
@@ -9535,7 +9578,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9553,7 +9596,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -9562,13 +9605,13 @@
         <v>38</v>
       </c>
       <c t="s" r="H264" s="8">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c t="s" r="I264" s="7">
         <v>56</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -9586,19 +9629,19 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G265" s="8">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c t="s" r="H265" s="8">
         <v>38</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c t="s" r="J265" s="7">
         <v>89</v>
@@ -9634,7 +9677,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -9643,17 +9686,19 @@
         <v>16</v>
       </c>
       <c t="s" r="H267" s="8">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c t="s" r="J267" s="7">
         <v>93</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
-      <c r="M267" s="7"/>
+      <c t="s" r="M267" s="7">
+        <v>325</v>
+      </c>
     </row>
     <row r="268" ht="14.25" customHeight="1">
       <c t="s" r="A268" s="6">
@@ -9667,13 +9712,13 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G268" s="8">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c t="s" r="H268" s="8">
         <v>16</v>
@@ -9700,7 +9745,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -9733,7 +9778,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -9745,7 +9790,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c t="s" r="J270" s="7">
         <v>138</v>
@@ -9781,7 +9826,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="F272" s="7">
         <v>320</v>
@@ -9790,10 +9835,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H272" s="8">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c t="s" r="J272" s="7">
         <v>143</v>
@@ -9801,7 +9846,7 @@
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
       <c t="s" r="M272" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="273" ht="14.25" customHeight="1">
@@ -9816,26 +9861,28 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="F273" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G273" s="8">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c t="s" r="H273" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c t="s" r="J273" s="7">
         <v>64</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
-      <c r="M273" s="7"/>
+      <c t="s" r="M273" s="7">
+        <v>329</v>
+      </c>
     </row>
     <row r="274" ht="14.25" customHeight="1">
       <c t="s" r="A274" s="6">
@@ -9849,7 +9896,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="F274" s="7">
         <v>320</v>
@@ -9882,7 +9929,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="F275" s="7">
         <v>320</v>
@@ -9915,7 +9962,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="F276" s="7">
         <v>320</v>
@@ -9924,7 +9971,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H276" s="8">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c t="s" r="I276" s="7">
         <v>138</v>
@@ -9948,19 +9995,19 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="F277" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G277" s="8">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c t="s" r="H277" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c t="s" r="J277" s="7">
         <v>149</v>
@@ -9981,7 +10028,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="F278" s="7">
         <v>320</v>
@@ -9993,10 +10040,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -10029,7 +10076,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -10038,7 +10085,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H280" s="8">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c t="s" r="I280" s="7">
         <v>31</v>
@@ -10062,13 +10109,13 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G281" s="8">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c t="s" r="H281" s="8">
         <v>16</v>
@@ -10095,7 +10142,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
@@ -10128,7 +10175,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
@@ -10140,10 +10187,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10161,7 +10208,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
@@ -10173,7 +10220,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c t="s" r="J284" s="7">
         <v>116</v>
@@ -10194,7 +10241,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
@@ -10206,10 +10253,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10242,19 +10289,19 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G287" s="8">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c t="s" r="H287" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c t="s" r="J287" s="7">
         <v>68</v>
@@ -10275,7 +10322,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -10290,7 +10337,7 @@
         <v>163</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -10308,7 +10355,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -10323,7 +10370,7 @@
         <v>175</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -10341,7 +10388,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -10353,10 +10400,10 @@
         <v>117</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10389,7 +10436,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="F292" s="7">
         <v>320</v>
@@ -10398,7 +10445,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H292" s="8">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c t="s" r="I292" s="7">
         <v>189</v>
@@ -10422,22 +10469,22 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="F293" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G293" s="8">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c t="s" r="H293" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10455,7 +10502,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
@@ -10467,7 +10514,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c t="s" r="J294" s="7">
         <v>84</v>
@@ -10488,7 +10535,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
@@ -10500,7 +10547,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c t="s" r="J295" s="7">
         <v>137</v>
@@ -10521,7 +10568,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
@@ -10536,7 +10583,7 @@
         <v>174</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -10554,7 +10601,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -10566,10 +10613,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -10602,7 +10649,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
@@ -10611,17 +10658,19 @@
         <v>50</v>
       </c>
       <c t="s" r="H299" s="8">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c t="s" r="J299" s="7">
         <v>19</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
-      <c r="M299" s="7"/>
+      <c t="s" r="M299" s="7">
+        <v>342</v>
+      </c>
     </row>
     <row r="300" ht="15" customHeight="1">
       <c t="s" r="A300" s="6">
@@ -10635,13 +10684,13 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G300" s="8">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c t="s" r="H300" s="8">
         <v>50</v>
@@ -10668,7 +10717,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
@@ -10683,7 +10732,7 @@
         <v>136</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>32</v>
+        <v>191</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10701,7 +10750,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="F302" s="7">
         <v>320</v>
@@ -10716,7 +10765,7 @@
         <v>65</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -10734,7 +10783,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="F303" s="7">
         <v>320</v>
@@ -10767,7 +10816,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="F304" s="7">
         <v>320</v>
@@ -10782,7 +10831,7 @@
         <v>69</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
@@ -10800,7 +10849,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
@@ -10815,7 +10864,7 @@
         <v>125</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -10833,7 +10882,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
@@ -10845,10 +10894,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -10881,7 +10930,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
@@ -10893,7 +10942,7 @@
         <v>130</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c t="s" r="J308" s="7">
         <v>159</v>
@@ -10914,7 +10963,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="F309" s="7">
         <v>321</v>
@@ -10926,7 +10975,7 @@
         <v>55</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="J309" s="7">
         <v>173</v>
@@ -10947,7 +10996,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="F310" s="7">
         <v>321</v>
@@ -10980,7 +11029,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="F311" s="7">
         <v>321</v>
@@ -10989,13 +11038,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -11013,19 +11062,19 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="F312" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c t="s" r="H312" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c t="s" r="J312" s="7">
         <v>88</v>
@@ -11046,7 +11095,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
@@ -11058,7 +11107,7 @@
         <v>38</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="J313" s="7">
         <v>141</v>
@@ -11079,7 +11128,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="F314" s="7">
         <v>321</v>
@@ -11091,10 +11140,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11127,7 +11176,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -11139,7 +11188,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c t="s" r="J316" s="7">
         <v>21</v>
@@ -11147,7 +11196,7 @@
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
       <c t="s" r="M316" s="7">
-        <v>342</v>
+        <v>349</v>
       </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
@@ -11162,7 +11211,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -11195,7 +11244,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
@@ -11210,7 +11259,7 @@
         <v>157</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11228,7 +11277,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
@@ -11243,7 +11292,7 @@
         <v>170</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
@@ -11261,7 +11310,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -11273,7 +11322,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c t="s" r="J320" s="7">
         <v>107</v>
@@ -11294,7 +11343,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
@@ -11306,10 +11355,10 @@
         <v>154</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -11327,7 +11376,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -11339,10 +11388,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -11375,7 +11424,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="F324" s="7">
         <v>321</v>
@@ -11387,10 +11436,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11408,7 +11457,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="F325" s="7">
         <v>321</v>
@@ -11420,7 +11469,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c t="s" r="J325" s="7">
         <v>76</v>
@@ -11441,7 +11490,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="F326" s="7">
         <v>321</v>
@@ -11453,7 +11502,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c t="s" r="J326" s="7">
         <v>36</v>
@@ -11474,7 +11523,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="F327" s="7">
         <v>321</v>
@@ -11507,7 +11556,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="F328" s="7">
         <v>321</v>
@@ -11519,7 +11568,7 @@
         <v>38</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c t="s" r="J328" s="7">
         <v>167</v>
@@ -11555,7 +11604,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
@@ -11564,17 +11613,19 @@
         <v>50</v>
       </c>
       <c t="s" r="H330" s="8">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c t="s" r="I330" s="7">
         <v>183</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>32</v>
+        <v>191</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
-      <c r="M330" s="7"/>
+      <c t="s" r="M330" s="7">
+        <v>358</v>
+      </c>
     </row>
     <row r="331" ht="14.25" customHeight="1">
       <c t="s" r="A331" s="6">
@@ -11588,13 +11639,13 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G331" s="8">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c t="s" r="H331" s="8">
         <v>50</v>
@@ -11621,7 +11672,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
@@ -11654,7 +11705,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -11669,7 +11720,7 @@
         <v>166</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -11702,7 +11753,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
@@ -11711,7 +11762,7 @@
         <v>50</v>
       </c>
       <c t="s" r="H335" s="8">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="I335" s="7">
         <v>101</v>
@@ -11735,19 +11786,19 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G336" s="8">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="H336" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c t="s" r="J336" s="7">
         <v>105</v>
@@ -11768,7 +11819,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="F337" s="7">
         <v>321</v>
@@ -11783,7 +11834,7 @@
         <v>66</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -11801,7 +11852,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
@@ -11816,7 +11867,7 @@
         <v>137</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
@@ -11834,7 +11885,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
@@ -11846,7 +11897,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c t="s" r="J339" s="7">
         <v>175</v>
@@ -11882,7 +11933,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -11894,7 +11945,7 @@
         <v>55</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c t="s" r="J341" s="7">
         <v>62</v>
@@ -11917,7 +11968,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
@@ -11929,7 +11980,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c t="s" r="J342" s="7">
         <v>178</v>
@@ -11950,7 +12001,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
@@ -11965,7 +12016,7 @@
         <v>75</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -11983,7 +12034,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
@@ -11995,7 +12046,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c t="s" r="J344" s="7">
         <v>66</v>
@@ -12016,7 +12067,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
@@ -12025,10 +12076,10 @@
         <v>50</v>
       </c>
       <c t="s" r="H345" s="8">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c t="s" r="J345" s="7">
         <v>134</v>
@@ -12049,13 +12100,13 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c t="s" r="H346" s="8">
         <v>50</v>
@@ -12064,7 +12115,7 @@
         <v>163</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12082,7 +12133,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
@@ -12097,7 +12148,7 @@
         <v>165</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12115,7 +12166,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
@@ -12130,7 +12181,7 @@
         <v>149</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12163,7 +12214,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
@@ -12178,12 +12229,12 @@
         <v>99</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
       <c t="s" r="M350" s="7">
-        <v>358</v>
+        <v>366</v>
       </c>
     </row>
     <row r="351" ht="14.25" customHeight="1">
@@ -12198,7 +12249,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
@@ -12217,7 +12268,9 @@
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
-      <c r="M351" s="7"/>
+      <c t="s" r="M351" s="7">
+        <v>367</v>
+      </c>
     </row>
     <row r="352" ht="14.25" customHeight="1">
       <c t="s" r="A352" s="6">
@@ -12231,7 +12284,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="F352" s="7">
         <v>320</v>
@@ -12246,7 +12299,7 @@
         <v>81</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
@@ -12264,7 +12317,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
@@ -12276,7 +12329,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c t="s" r="J353" s="7">
         <v>76</v>
@@ -12297,7 +12350,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
@@ -12309,7 +12362,7 @@
         <v>38</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c t="s" r="J354" s="7">
         <v>96</v>
@@ -12330,7 +12383,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
@@ -12342,7 +12395,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c t="s" r="J355" s="7">
         <v>86</v>
@@ -12363,7 +12416,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
@@ -12375,7 +12428,7 @@
         <v>38</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="J356" s="7">
         <v>39</v>
@@ -12396,7 +12449,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
@@ -12408,7 +12461,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="J357" s="7">
         <v>141</v>
@@ -12444,7 +12497,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -12456,14 +12509,16 @@
         <v>16</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c t="s" r="J359" s="7">
         <v>64</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
-      <c r="M359" s="7"/>
+      <c t="s" r="M359" s="7">
+        <v>371</v>
+      </c>
     </row>
     <row r="360" ht="15" customHeight="1">
       <c t="s" r="A360" s="6">
@@ -12477,7 +12532,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -12510,7 +12565,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -12522,10 +12577,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12543,7 +12598,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -12576,7 +12631,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -12591,7 +12646,7 @@
         <v>115</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -12624,7 +12679,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="F365" s="7">
         <v>320</v>
@@ -12639,11 +12694,13 @@
         <v>101</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
-      <c r="M365" s="7"/>
+      <c t="s" r="M365" s="7">
+        <v>374</v>
+      </c>
     </row>
     <row r="366" ht="14.25" customHeight="1">
       <c t="s" r="A366" s="6">
@@ -12657,7 +12714,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="F366" s="7">
         <v>320</v>
@@ -12672,7 +12729,7 @@
         <v>102</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12690,7 +12747,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
@@ -12723,7 +12780,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
@@ -12738,7 +12795,7 @@
         <v>36</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -12756,7 +12813,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
@@ -12768,10 +12825,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -12804,7 +12861,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="F371" s="7">
         <v>320</v>
@@ -12816,10 +12873,10 @@
         <v>171</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -12837,7 +12894,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
@@ -12849,7 +12906,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c t="s" r="J372" s="7">
         <v>65</v>
@@ -12870,7 +12927,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="F373" s="7">
         <v>320</v>
@@ -12885,7 +12942,7 @@
         <v>123</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -12903,7 +12960,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="F374" s="7">
         <v>320</v>
@@ -12915,10 +12972,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -12936,7 +12993,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="F375" s="7">
         <v>320</v>
@@ -12951,7 +13008,7 @@
         <v>56</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -12969,7 +13026,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="F376" s="7">
         <v>320</v>
@@ -12981,10 +13038,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -13017,7 +13074,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
@@ -13032,7 +13089,7 @@
         <v>156</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -13050,7 +13107,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
@@ -13062,10 +13119,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>32</v>
+        <v>191</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13083,7 +13140,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
@@ -13092,10 +13149,10 @@
         <v>50</v>
       </c>
       <c t="s" r="H380" s="8">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="J380" s="7">
         <v>174</v>
@@ -13116,19 +13173,19 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G381" s="8">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c t="s" r="H381" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c t="s" r="J381" s="7">
         <v>25</v>
@@ -13149,7 +13206,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -13197,7 +13254,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -13209,10 +13266,10 @@
         <v>51</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13230,7 +13287,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -13263,7 +13320,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
@@ -13272,13 +13329,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H386" s="8">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13296,22 +13353,22 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G387" s="8">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c t="s" r="H387" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13344,13 +13401,13 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="F389" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G389" s="8">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c t="s" r="H389" s="8">
         <v>50</v>
@@ -13377,7 +13434,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
@@ -13392,7 +13449,7 @@
         <v>85</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -13410,7 +13467,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="F391" s="7">
         <v>320</v>
@@ -13422,7 +13479,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c t="s" r="J391" s="7">
         <v>140</v>
@@ -13458,7 +13515,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="F393" s="7">
         <v>320</v>
@@ -13477,7 +13534,9 @@
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
-      <c r="M393" s="7"/>
+      <c t="s" r="M393" s="7">
+        <v>389</v>
+      </c>
     </row>
     <row r="394" ht="14.25" customHeight="1">
       <c t="s" r="A394" s="6">
@@ -13491,7 +13550,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="F394" s="7">
         <v>320</v>
@@ -13503,10 +13562,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -13524,7 +13583,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="F395" s="7">
         <v>320</v>
@@ -13536,7 +13595,7 @@
         <v>180</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c t="s" r="J395" s="7">
         <v>83</v>
@@ -13557,7 +13616,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="F396" s="7">
         <v>320</v>
@@ -13572,7 +13631,7 @@
         <v>122</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -13590,7 +13649,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="F397" s="7">
         <v>320</v>
@@ -13599,13 +13658,13 @@
         <v>50</v>
       </c>
       <c t="s" r="H397" s="8">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c t="s" r="I397" s="7">
         <v>36</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -13623,22 +13682,22 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="F398" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G398" s="8">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c t="s" r="H398" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13671,7 +13730,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
@@ -13691,7 +13750,7 @@
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
       <c t="s" r="M400" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="401" ht="14.25" customHeight="1">
@@ -13706,7 +13765,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
@@ -13739,7 +13798,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="F402" s="7">
         <v>321</v>
@@ -13754,7 +13813,7 @@
         <v>169</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
@@ -13772,7 +13831,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
@@ -13784,10 +13843,10 @@
         <v>38</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
@@ -13805,7 +13864,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
@@ -13817,7 +13876,7 @@
         <v>180</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c t="s" r="J404" s="7">
         <v>106</v>
@@ -13838,7 +13897,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
@@ -13853,7 +13912,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -13871,7 +13930,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
@@ -13886,7 +13945,7 @@
         <v>54</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
@@ -13904,7 +13963,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
@@ -13919,7 +13978,7 @@
         <v>166</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -13937,7 +13996,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="F408" s="7">
         <v>321</v>
@@ -13949,10 +14008,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -13985,7 +14044,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="F410" s="7">
         <v>321</v>
@@ -13997,15 +14056,15 @@
         <v>50</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
       <c t="s" r="M410" s="7">
-        <v>382</v>
+        <v>394</v>
       </c>
     </row>
     <row r="411" ht="14.25" customHeight="1">
@@ -14020,7 +14079,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
@@ -14032,7 +14091,7 @@
         <v>190</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c t="s" r="J411" s="7">
         <v>65</v>
@@ -14053,7 +14112,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="F412" s="7">
         <v>321</v>
@@ -14086,7 +14145,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="F413" s="7">
         <v>321</v>
@@ -14098,10 +14157,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
@@ -14119,7 +14178,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="F414" s="7">
         <v>321</v>
@@ -14128,13 +14187,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H414" s="8">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -14152,22 +14211,22 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="F415" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G415" s="8">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c t="s" r="H415" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
@@ -14200,7 +14259,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="F417" s="7">
         <v>321</v>
@@ -14233,7 +14292,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
@@ -14266,7 +14325,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="F419" s="7">
         <v>321</v>
@@ -14278,10 +14337,10 @@
         <v>154</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
@@ -14299,7 +14358,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="F420" s="7">
         <v>321</v>
@@ -14314,7 +14373,7 @@
         <v>68</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -14332,7 +14391,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="F421" s="7">
         <v>321</v>
@@ -14344,10 +14403,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
@@ -14365,7 +14424,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="F422" s="7">
         <v>321</v>
@@ -14377,10 +14436,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c t="s" r="J422" s="7">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
@@ -14413,7 +14472,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="F424" s="7">
         <v>321</v>
@@ -14422,10 +14481,10 @@
         <v>50</v>
       </c>
       <c t="s" r="H424" s="8">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c t="s" r="J424" s="7">
         <v>121</v>
@@ -14446,22 +14505,22 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="F425" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G425" s="8">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c t="s" r="H425" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
@@ -14479,7 +14538,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="F426" s="7">
         <v>321</v>
@@ -14488,20 +14547,20 @@
         <v>50</v>
       </c>
       <c t="s" r="H426" s="8">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c t="s" r="I426" s="7">
         <v>157</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c t="s" r="K426" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L426" s="7"/>
       <c t="s" r="M426" s="7">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="427" ht="14.25" customHeight="1">
@@ -14516,19 +14575,19 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="F427" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G427" s="8">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c t="s" r="H427" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c t="s" r="J427" s="7">
         <v>77</v>
@@ -14538,7 +14597,7 @@
       </c>
       <c r="L427" s="7"/>
       <c t="s" r="M427" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="428" ht="14.25" customHeight="1">
@@ -14568,7 +14627,7 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="F429" s="7">
         <v>321</v>
@@ -14583,11 +14642,13 @@
         <v>79</v>
       </c>
       <c t="s" r="J429" s="7">
-        <v>392</v>
+        <v>374</v>
       </c>
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
-      <c r="M429" s="7"/>
+      <c t="s" r="M429" s="7">
+        <v>404</v>
+      </c>
     </row>
     <row r="430" ht="15" customHeight="1">
       <c t="s" r="A430" s="6">
@@ -14601,7 +14662,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="F430" s="7">
         <v>321</v>
@@ -14613,7 +14674,7 @@
         <v>38</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>392</v>
+        <v>374</v>
       </c>
       <c t="s" r="J430" s="7">
         <v>75</v>
@@ -14623,7 +14684,7 @@
       </c>
       <c r="L430" s="7"/>
       <c t="s" r="M430" s="7">
-        <v>359</v>
+        <v>368</v>
       </c>
     </row>
     <row r="431" ht="14.25" customHeight="1">
@@ -14638,7 +14699,7 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="F431" s="7">
         <v>321</v>
@@ -14653,14 +14714,14 @@
         <v>146</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c t="s" r="K431" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L431" s="7"/>
       <c t="s" r="M431" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="432" ht="14.25" customHeight="1">
@@ -14675,7 +14736,7 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="F432" s="7">
         <v>321</v>
@@ -14687,7 +14748,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I432" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c t="s" r="J432" s="7">
         <v>137</v>
@@ -14708,7 +14769,7 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="F433" s="7">
         <v>321</v>
@@ -14720,10 +14781,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I433" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
@@ -14741,7 +14802,7 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="F434" s="7">
         <v>321</v>
@@ -14750,13 +14811,13 @@
         <v>50</v>
       </c>
       <c t="s" r="H434" s="8">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c t="s" r="I434" s="7">
         <v>141</v>
       </c>
       <c t="s" r="J434" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
@@ -14774,22 +14835,22 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="F435" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G435" s="8">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c t="s" r="H435" s="8">
         <v>50</v>
       </c>
       <c t="s" r="I435" s="7">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c t="s" r="J435" s="7">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="K435" s="7"/>
       <c r="L435" s="7"/>
@@ -14822,7 +14883,7 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="F437" s="7">
         <v>320</v>
@@ -14837,7 +14898,7 @@
         <v>121</v>
       </c>
       <c t="s" r="J437" s="7">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
@@ -14855,7 +14916,7 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="F438" s="7">
         <v>320</v>
@@ -14867,7 +14928,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I438" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="J438" s="7">
         <v>76</v>
@@ -14888,7 +14949,7 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="F439" s="7">
         <v>320</v>
@@ -14921,7 +14982,7 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="F440" s="7">
         <v>320</v>
@@ -14954,7 +15015,7 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="F441" s="7">
         <v>320</v>
@@ -14966,10 +15027,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I441" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="J441" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
@@ -14987,7 +15048,7 @@
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="F442" s="7">
         <v>320</v>
@@ -14999,10 +15060,10 @@
         <v>50</v>
       </c>
       <c t="s" r="I442" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c t="s" r="J442" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K442" s="7"/>
       <c r="L442" s="7"/>
@@ -15035,7 +15096,7 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="F444" s="7">
         <v>321</v>
@@ -15047,7 +15108,7 @@
         <v>55</v>
       </c>
       <c t="s" r="I444" s="7">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c t="s" r="J444" s="7">
         <v>52</v>
@@ -15055,7 +15116,7 @@
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
       <c t="s" r="M444" s="7">
-        <v>396</v>
+        <v>408</v>
       </c>
     </row>
     <row r="445" ht="15" customHeight="1">
@@ -15070,7 +15131,7 @@
       </c>
       <c r="D445" s="7"/>
       <c t="s" r="E445" s="7">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="F445" s="7">
         <v>321</v>
@@ -15085,7 +15146,7 @@
         <v>111</v>
       </c>
       <c t="s" r="J445" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K445" s="7"/>
       <c r="L445" s="7"/>
@@ -15103,7 +15164,7 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="F446" s="7">
         <v>321</v>
@@ -15118,7 +15179,7 @@
         <v>114</v>
       </c>
       <c t="s" r="J446" s="7">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>
@@ -15136,7 +15197,7 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="F447" s="7">
         <v>321</v>
@@ -15151,7 +15212,7 @@
         <v>116</v>
       </c>
       <c t="s" r="J447" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="K447" s="7"/>
       <c r="L447" s="7"/>
@@ -15184,7 +15245,7 @@
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="F449" s="7">
         <v>321</v>
@@ -15196,7 +15257,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I449" s="7">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c t="s" r="J449" s="7">
         <v>107</v>
@@ -15217,7 +15278,7 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="F450" s="7">
         <v>321</v>
@@ -15229,10 +15290,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I450" s="7">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c t="s" r="J450" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K450" s="7"/>
       <c r="L450" s="7"/>
@@ -15250,7 +15311,7 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="F451" s="7">
         <v>321</v>
@@ -15262,10 +15323,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I451" s="7">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c t="s" r="J451" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K451" s="7"/>
       <c r="L451" s="7"/>
@@ -15283,7 +15344,7 @@
       </c>
       <c r="D452" s="7"/>
       <c t="s" r="E452" s="7">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="F452" s="7">
         <v>321</v>
@@ -15295,7 +15356,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I452" s="7">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c t="s" r="J452" s="7">
         <v>89</v>
@@ -15316,7 +15377,7 @@
       </c>
       <c r="D453" s="7"/>
       <c t="s" r="E453" s="7">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="F453" s="7">
         <v>321</v>
@@ -15328,10 +15389,10 @@
         <v>23</v>
       </c>
       <c t="s" r="I453" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J453" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K453" s="7"/>
       <c r="L453" s="7"/>
@@ -15364,7 +15425,7 @@
       </c>
       <c r="D455" s="7"/>
       <c t="s" r="E455" s="7">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="F455" s="7">
         <v>320</v>
@@ -15373,18 +15434,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H455" s="8">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c t="s" r="I455" s="7">
         <v>58</v>
       </c>
       <c t="s" r="J455" s="7">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K455" s="7"/>
       <c r="L455" s="7"/>
       <c t="s" r="M455" s="7">
-        <v>400</v>
+        <v>412</v>
       </c>
     </row>
     <row r="456" ht="14.25" customHeight="1">
@@ -15399,13 +15460,13 @@
       </c>
       <c r="D456" s="7"/>
       <c t="s" r="E456" s="7">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="F456" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G456" s="8">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c t="s" r="H456" s="8">
         <v>16</v>
@@ -15414,7 +15475,7 @@
         <v>128</v>
       </c>
       <c t="s" r="J456" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K456" s="7"/>
       <c r="L456" s="7"/>
@@ -15432,7 +15493,7 @@
       </c>
       <c r="D457" s="7"/>
       <c t="s" r="E457" s="7">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="F457" s="7">
         <v>320</v>
@@ -15465,7 +15526,7 @@
       </c>
       <c r="D458" s="7"/>
       <c t="s" r="E458" s="7">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="F458" s="7">
         <v>320</v>
@@ -15480,7 +15541,7 @@
         <v>132</v>
       </c>
       <c t="s" r="J458" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K458" s="7"/>
       <c r="L458" s="7"/>
@@ -15498,7 +15559,7 @@
       </c>
       <c r="D459" s="7"/>
       <c t="s" r="E459" s="7">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="F459" s="7">
         <v>320</v>
@@ -15507,13 +15568,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H459" s="8">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c t="s" r="I459" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="J459" s="7">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="K459" s="7"/>
       <c r="L459" s="7"/>
@@ -15531,13 +15592,13 @@
       </c>
       <c r="D460" s="7"/>
       <c t="s" r="E460" s="7">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="F460" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G460" s="8">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c t="s" r="H460" s="8">
         <v>16</v>
@@ -15564,7 +15625,7 @@
       </c>
       <c r="D461" s="7"/>
       <c t="s" r="E461" s="7">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="F461" s="7">
         <v>320</v>
@@ -15573,13 +15634,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H461" s="8">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c t="s" r="I461" s="7">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c t="s" r="J461" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K461" s="7"/>
       <c r="L461" s="7"/>
@@ -15597,13 +15658,13 @@
       </c>
       <c r="D462" s="7"/>
       <c t="s" r="E462" s="7">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="F462" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G462" s="8">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c t="s" r="H462" s="8">
         <v>16</v>
@@ -15612,7 +15673,7 @@
         <v>56</v>
       </c>
       <c t="s" r="J462" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K462" s="7"/>
       <c r="L462" s="7"/>
@@ -15645,7 +15706,7 @@
       </c>
       <c r="D464" s="7"/>
       <c t="s" r="E464" s="7">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="F464" s="7">
         <v>330</v>
@@ -15657,7 +15718,7 @@
         <v>55</v>
       </c>
       <c t="s" r="I464" s="7">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c t="s" r="J464" s="7">
         <v>170</v>
@@ -15678,7 +15739,7 @@
       </c>
       <c r="D465" s="7"/>
       <c t="s" r="E465" s="7">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="F465" s="7">
         <v>330</v>
@@ -15687,7 +15748,7 @@
         <v>55</v>
       </c>
       <c t="s" r="H465" s="8">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c t="s" r="I465" s="7">
         <v>163</v>
@@ -15711,19 +15772,19 @@
       </c>
       <c r="D466" s="7"/>
       <c t="s" r="E466" s="7">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="F466" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G466" s="8">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c t="s" r="H466" s="8">
         <v>55</v>
       </c>
       <c t="s" r="I466" s="7">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c t="s" r="J466" s="7">
         <v>110</v>
@@ -15759,7 +15820,7 @@
       </c>
       <c r="D468" s="7"/>
       <c t="s" r="E468" s="7">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="F468" s="7">
         <v>330</v>
@@ -15771,7 +15832,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I468" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c t="s" r="J468" s="7">
         <v>102</v>
@@ -15792,7 +15853,7 @@
       </c>
       <c r="D469" s="7"/>
       <c t="s" r="E469" s="7">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="F469" s="7">
         <v>330</v>
@@ -15804,10 +15865,10 @@
         <v>55</v>
       </c>
       <c t="s" r="I469" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="J469" s="7">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="K469" s="7"/>
       <c r="L469" s="7"/>
@@ -15825,7 +15886,7 @@
       </c>
       <c r="D470" s="7"/>
       <c t="s" r="E470" s="7">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="F470" s="7">
         <v>330</v>
@@ -15834,17 +15895,21 @@
         <v>55</v>
       </c>
       <c t="s" r="H470" s="8">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c t="s" r="I470" s="7">
-        <v>32</v>
+        <v>191</v>
       </c>
       <c t="s" r="J470" s="7">
-        <v>336</v>
-      </c>
-      <c r="K470" s="7"/>
+        <v>343</v>
+      </c>
+      <c t="s" r="K470" s="7">
+        <v>239</v>
+      </c>
       <c r="L470" s="7"/>
-      <c r="M470" s="7"/>
+      <c t="s" r="M470" s="7">
+        <v>322</v>
+      </c>
     </row>
     <row r="471" ht="14.25" customHeight="1">
       <c t="s" r="A471" s="6">
@@ -15858,13 +15923,13 @@
       </c>
       <c r="D471" s="7"/>
       <c t="s" r="E471" s="7">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="F471" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G471" s="8">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c t="s" r="H471" s="8">
         <v>55</v>
@@ -15873,11 +15938,15 @@
         <v>126</v>
       </c>
       <c t="s" r="J471" s="7">
-        <v>278</v>
-      </c>
-      <c r="K471" s="7"/>
+        <v>280</v>
+      </c>
+      <c t="s" r="K471" s="7">
+        <v>418</v>
+      </c>
       <c r="L471" s="7"/>
-      <c r="M471" s="7"/>
+      <c t="s" r="M471" s="7">
+        <v>84</v>
+      </c>
     </row>
     <row r="472" ht="14.25" customHeight="1">
       <c r="A472" s="6"/>
@@ -15906,7 +15975,7 @@
       </c>
       <c r="D473" s="7"/>
       <c t="s" r="E473" s="7">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="F473" s="7">
         <v>330</v>
@@ -15918,7 +15987,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I473" s="7">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c t="s" r="J473" s="7">
         <v>24</v>
@@ -15939,7 +16008,7 @@
       </c>
       <c r="D474" s="7"/>
       <c t="s" r="E474" s="7">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="F474" s="7">
         <v>330</v>
@@ -15954,7 +16023,7 @@
         <v>105</v>
       </c>
       <c t="s" r="J474" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K474" s="7"/>
       <c r="L474" s="7"/>
@@ -15972,7 +16041,7 @@
       </c>
       <c r="D475" s="7"/>
       <c t="s" r="E475" s="7">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="F475" s="7">
         <v>330</v>
@@ -15987,7 +16056,7 @@
         <v>96</v>
       </c>
       <c t="s" r="J475" s="7">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="K475" s="7"/>
       <c r="L475" s="7"/>
@@ -16020,13 +16089,13 @@
       </c>
       <c r="D477" s="7"/>
       <c t="s" r="E477" s="7">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="F477" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G477" s="8">
-        <v>408</v>
+        <v>421</v>
       </c>
       <c t="s" r="H477" s="8">
         <v>16</v>
@@ -16053,7 +16122,7 @@
       </c>
       <c r="D478" s="7"/>
       <c t="s" r="E478" s="7">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="F478" s="7">
         <v>330</v>
@@ -16062,13 +16131,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H478" s="8">
-        <v>408</v>
+        <v>421</v>
       </c>
       <c t="s" r="I478" s="7">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c t="s" r="J478" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="K478" s="7"/>
       <c r="L478" s="7"/>
@@ -16101,7 +16170,7 @@
       </c>
       <c r="D480" s="7"/>
       <c t="s" r="E480" s="7">
-        <v>409</v>
+        <v>422</v>
       </c>
       <c r="F480" s="7">
         <v>330</v>
@@ -16110,13 +16179,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H480" s="8">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c t="s" r="I480" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="J480" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K480" s="7"/>
       <c r="L480" s="7"/>
@@ -16134,13 +16203,13 @@
       </c>
       <c r="D481" s="7"/>
       <c t="s" r="E481" s="7">
-        <v>409</v>
+        <v>422</v>
       </c>
       <c r="F481" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G481" s="8">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c t="s" r="H481" s="8">
         <v>16</v>
@@ -16149,7 +16218,7 @@
         <v>27</v>
       </c>
       <c t="s" r="J481" s="7">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="K481" s="7"/>
       <c r="L481" s="7"/>
@@ -16157,7 +16226,7 @@
     </row>
     <row r="482" ht="15.75" customHeight="1">
       <c t="s" r="A482" s="9">
-        <v>411</v>
+        <v>424</v>
       </c>
       <c r="B482" s="9"/>
       <c r="C482" s="9"/>
@@ -16177,7 +16246,7 @@
     <row r="483" ht="65.25" customHeight="1"/>
     <row r="484" ht="16.5" customHeight="1">
       <c t="s" r="A484" s="10">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="B484" s="10"/>
       <c r="C484" s="10"/>
@@ -16190,7 +16259,7 @@
       <c r="J484" s="10"/>
       <c r="K484" s="10"/>
       <c t="s" r="L484" s="11">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="M484" s="11"/>
       <c r="N484" s="11"/>
